--- a/request_forms/050_driving_record_request_form--request_forms.xlsx
+++ b/request_forms/050_driving_record_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mi</t>
+          <t>mo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>mo</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MS</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>mt</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mt</t>
+          <t>ne</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>NE</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ne</t>
+          <t>oh</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>OH</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>oh</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OR</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>pa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>PA</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>pa</t>
+          <t>sc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SC</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>tn</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TN</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>tn</t>
+          <t>tx</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>TX</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>tx</t>
+          <t>ut</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>UT</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ut</t>
+          <t>va</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>VA</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>va</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>WA</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>wa</t>
+          <t>wi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>WI</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>wi</t>
+          <t>wv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>WI</t>
+          <t>WV</t>
         </is>
       </c>
     </row>
@@ -1573,29 +1573,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wv</t>
+          <t>wy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>WV</t>
+          <t>WY</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>driver_license_state_choices</t>
+          <t>driver_license_type_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>wy</t>
+          <t>class_a</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>Class A</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>class_a</t>
+          <t>class_b</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Class A</t>
+          <t>Class B</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>class_b</t>
+          <t>class_c</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Class B</t>
+          <t>Class C</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>class_c</t>
+          <t>class_d</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Class C</t>
+          <t>Class D</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>class_d</t>
+          <t>class_e</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Class D</t>
+          <t>Class E</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>class_e</t>
+          <t>class_f</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Class E</t>
+          <t>Class F</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>class_f</t>
+          <t>class_g</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Class F</t>
+          <t>Class G</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>class_g</t>
+          <t>class_h</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Class G</t>
+          <t>Class H</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>class_h</t>
+          <t>class_i</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Class H</t>
+          <t>Class I</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>class_i</t>
+          <t>class_r</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Class I</t>
+          <t>Class R</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>class_r</t>
+          <t>class_r-ii</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Class R</t>
+          <t>Class R-II</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>class_r-ii</t>
+          <t>class_r-iii</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Class R-II</t>
+          <t>Class R-III</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>class_r-iii</t>
+          <t>class_r-iv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Class R-III</t>
+          <t>Class R-IV</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>class_r-iv</t>
+          <t>class_r-nd</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Class R-IV</t>
+          <t>Class R-ND</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>class_r-nd</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Class R-ND</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>commercial</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Motorcycle</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>motorcycle</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>private</t>
+          <t>school_bus</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>School Bus</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>school_bus</t>
+          <t>taxicab</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>School Bus</t>
+          <t>Taxicab</t>
         </is>
       </c>
     </row>
@@ -1913,27 +1913,10 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>taxicab</t>
+          <t>tractor-plate</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
-        <is>
-          <t>Taxicab</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>driver_license_type_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>tractor-plate</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
         <is>
           <t>Tractor-Plate</t>
         </is>
